--- a/_Learn/Packaging.tutorial/OS.11/24H2/Expand/Install/Report.Overview.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/24H2/Expand/Install/Report.Overview.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\24H2\Expand\Install\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25DCE71-4B82-4F81-8FBB-E3F521A7ABE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3821B17C-4E52-4A3D-A7FC-9562CCC04B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report.Overview" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="116">
   <si>
     <t>Verify if it is published by Yi</t>
   </si>
@@ -610,6 +610,19 @@
   </si>
   <si>
     <t>Download the full report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+en-US
+ar-EG
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+Microsoft-Windows-LanguageFeatures-TextToSpeech-ar-eg-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+</t>
   </si>
 </sst>
 </file>
@@ -992,12 +1005,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="10" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="14" fillId="12" borderId="0" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1007,6 +1014,12 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="20">
@@ -1049,6 +1062,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1075,7 +1089,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1826,8 +1839,8 @@
     <tableColumn id="6" xr3:uid="{29C36E64-2197-4F42-9311-FC2C64933C3B}" name="Image Languages" dataDxfId="4"/>
     <tableColumn id="7" xr3:uid="{790C3054-26A7-41A6-ADE6-EA6C42B90B32}" name="Installed Packages" dataDxfId="3"/>
     <tableColumn id="8" xr3:uid="{AD14BA4A-B159-4A19-B091-C7CA064CB363}" name="InBox Apps" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{374A85F7-5A11-4409-8BF3-8A3E7E0DF6E4}" name="Github" dataDxfId="0"/>
-    <tableColumn id="9" xr3:uid="{22D640C2-148E-4921-B4C9-91F530651217}" name="Remark" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{374A85F7-5A11-4409-8BF3-8A3E7E0DF6E4}" name="Github" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{22D640C2-148E-4921-B4C9-91F530651217}" name="Remark" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Home Inventory" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2010,24 +2023,24 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N70"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="84.69140625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="50.3828125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="20.53515625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="16.69140625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="120.69140625" style="6" customWidth="1"/>
-    <col min="9" max="11" width="16.69140625" style="6" customWidth="1"/>
-    <col min="12" max="12" width="25.69140625" style="6" customWidth="1"/>
-    <col min="13" max="13" width="16.69140625" style="10" customWidth="1"/>
-    <col min="14" max="14" width="2.69140625" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="9.15234375" style="4" hidden="1"/>
+    <col min="1" max="1" width="2.6640625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="84.6640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="50.3984375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="20.53125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="120.6640625" style="6" customWidth="1"/>
+    <col min="9" max="11" width="16.6640625" style="6" customWidth="1"/>
+    <col min="12" max="12" width="25.6640625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" style="10" customWidth="1"/>
+    <col min="14" max="14" width="2.6640625" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="9.1328125" style="4" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="4"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2042,7 +2055,7 @@
       <c r="L1" s="5"/>
       <c r="M1" s="4"/>
     </row>
-    <row r="2" spans="1:14" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" ht="80.2" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="4"/>
       <c r="C2" s="20" t="s">
         <v>70</v>
@@ -2051,17 +2064,17 @@
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="22" t="s">
         <v>48</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="5"/>
-      <c r="L2" s="24" t="s">
+      <c r="L2" s="22" t="s">
         <v>113</v>
       </c>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="4"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -2075,7 +2088,7 @@
       <c r="L3" s="5"/>
       <c r="M3" s="4"/>
     </row>
-    <row r="4" spans="1:14" ht="5.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" ht="5.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -2086,9 +2099,9 @@
       <c r="I4" s="11"/>
       <c r="J4" s="12"/>
       <c r="K4" s="13"/>
-      <c r="L4" s="23"/>
-    </row>
-    <row r="5" spans="1:14" ht="62.7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L4" s="21"/>
+    </row>
+    <row r="5" spans="1:14" ht="62.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="14"/>
       <c r="C5" s="14" t="s">
         <v>7</v>
@@ -2125,7 +2138,7 @@
       </c>
       <c r="N5" s="10"/>
     </row>
-    <row r="6" spans="1:14" ht="396.45" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" ht="393.75" x14ac:dyDescent="0.45">
       <c r="B6" s="2"/>
       <c r="C6" s="6">
         <v>1</v>
@@ -2152,13 +2165,13 @@
       <c r="K6" s="2">
         <v>1</v>
       </c>
-      <c r="L6" s="25" t="s">
+      <c r="L6" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="10"/>
     </row>
-    <row r="7" spans="1:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B7" s="2"/>
       <c r="C7" s="6">
         <v>2</v>
@@ -2173,10 +2186,10 @@
         <v>6</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -2187,13 +2200,13 @@
       <c r="K7" s="2">
         <v>1</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="L7" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="10"/>
     </row>
-    <row r="8" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B8" s="2"/>
       <c r="C8" s="6">
         <v>3</v>
@@ -2222,13 +2235,13 @@
       <c r="K8" s="2">
         <v>1</v>
       </c>
-      <c r="L8" s="25" t="s">
+      <c r="L8" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="10"/>
     </row>
-    <row r="9" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B9" s="2"/>
       <c r="C9" s="6">
         <v>4</v>
@@ -2255,13 +2268,13 @@
       <c r="K9" s="2">
         <v>1</v>
       </c>
-      <c r="L9" s="25" t="s">
+      <c r="L9" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="10"/>
     </row>
-    <row r="10" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B10" s="2"/>
       <c r="C10" s="6">
         <v>5</v>
@@ -2290,13 +2303,13 @@
       <c r="K10" s="2">
         <v>1</v>
       </c>
-      <c r="L10" s="25" t="s">
+      <c r="L10" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="10"/>
     </row>
-    <row r="11" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B11" s="2"/>
       <c r="C11" s="6">
         <v>6</v>
@@ -2323,13 +2336,13 @@
       <c r="K11" s="2">
         <v>1</v>
       </c>
-      <c r="L11" s="25" t="s">
+      <c r="L11" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B12" s="2"/>
       <c r="C12" s="6">
         <v>7</v>
@@ -2358,13 +2371,13 @@
       <c r="K12" s="2">
         <v>1</v>
       </c>
-      <c r="L12" s="25" t="s">
+      <c r="L12" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="10"/>
     </row>
-    <row r="13" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B13" s="2"/>
       <c r="C13" s="6">
         <v>8</v>
@@ -2391,13 +2404,13 @@
       <c r="K13" s="2">
         <v>1</v>
       </c>
-      <c r="L13" s="25" t="s">
+      <c r="L13" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="1:14" ht="253.75" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:14" ht="252" x14ac:dyDescent="0.45">
       <c r="B14" s="2"/>
       <c r="C14" s="6">
         <v>9</v>
@@ -2424,13 +2437,13 @@
       <c r="K14" s="2">
         <v>1</v>
       </c>
-      <c r="L14" s="25" t="s">
+      <c r="L14" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="1:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B15" s="2"/>
       <c r="C15" s="6">
         <v>10</v>
@@ -2457,13 +2470,13 @@
       <c r="K15" s="2">
         <v>1</v>
       </c>
-      <c r="L15" s="25" t="s">
+      <c r="L15" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B16" s="2"/>
       <c r="C16" s="6">
         <v>11</v>
@@ -2490,13 +2503,13 @@
       <c r="K16" s="2">
         <v>1</v>
       </c>
-      <c r="L16" s="25" t="s">
+      <c r="L16" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B17" s="2"/>
       <c r="C17" s="6">
         <v>12</v>
@@ -2523,13 +2536,13 @@
       <c r="K17" s="2">
         <v>1</v>
       </c>
-      <c r="L17" s="25" t="s">
+      <c r="L17" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="1:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B18" s="2"/>
       <c r="C18" s="6">
         <v>13</v>
@@ -2558,13 +2571,13 @@
       <c r="K18" s="2">
         <v>1</v>
       </c>
-      <c r="L18" s="25" t="s">
+      <c r="L18" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="1:14" ht="253.75" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:14" ht="252" x14ac:dyDescent="0.45">
       <c r="B19" s="2"/>
       <c r="C19" s="6">
         <v>14</v>
@@ -2591,13 +2604,13 @@
       <c r="K19" s="2">
         <v>1</v>
       </c>
-      <c r="L19" s="25" t="s">
+      <c r="L19" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="1:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B20" s="2"/>
       <c r="C20" s="6">
         <v>15</v>
@@ -2626,13 +2639,13 @@
       <c r="K20" s="2">
         <v>1</v>
       </c>
-      <c r="L20" s="25" t="s">
+      <c r="L20" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="10"/>
     </row>
-    <row r="21" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B21" s="2"/>
       <c r="C21" s="6">
         <v>16</v>
@@ -2659,13 +2672,13 @@
       <c r="K21" s="2">
         <v>1</v>
       </c>
-      <c r="L21" s="25" t="s">
+      <c r="L21" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B22" s="2"/>
       <c r="C22" s="6">
         <v>17</v>
@@ -2692,13 +2705,13 @@
       <c r="K22" s="2">
         <v>1</v>
       </c>
-      <c r="L22" s="25" t="s">
+      <c r="L22" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B23" s="2"/>
       <c r="C23" s="6">
         <v>18</v>
@@ -2725,13 +2738,13 @@
       <c r="K23" s="2">
         <v>1</v>
       </c>
-      <c r="L23" s="25" t="s">
+      <c r="L23" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="1:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B24" s="2"/>
       <c r="C24" s="6">
         <v>19</v>
@@ -2758,13 +2771,13 @@
       <c r="K24" s="2">
         <v>1</v>
       </c>
-      <c r="L24" s="25" t="s">
+      <c r="L24" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="10"/>
     </row>
-    <row r="25" spans="1:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B25" s="2"/>
       <c r="C25" s="6">
         <v>20</v>
@@ -2791,13 +2804,13 @@
       <c r="K25" s="2">
         <v>1</v>
       </c>
-      <c r="L25" s="25" t="s">
+      <c r="L25" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="10"/>
     </row>
-    <row r="26" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B26" s="2"/>
       <c r="C26" s="6">
         <v>21</v>
@@ -2824,13 +2837,13 @@
       <c r="K26" s="2">
         <v>1</v>
       </c>
-      <c r="L26" s="25" t="s">
+      <c r="L26" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="10"/>
     </row>
-    <row r="27" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B27" s="2"/>
       <c r="C27" s="6">
         <v>22</v>
@@ -2857,13 +2870,13 @@
       <c r="K27" s="2">
         <v>1</v>
       </c>
-      <c r="L27" s="25" t="s">
+      <c r="L27" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="10"/>
     </row>
-    <row r="28" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="A28" s="10" t="s">
         <v>61</v>
       </c>
@@ -2893,13 +2906,13 @@
       <c r="K28" s="2">
         <v>1</v>
       </c>
-      <c r="L28" s="25" t="s">
+      <c r="L28" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="10"/>
     </row>
-    <row r="29" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B29" s="2"/>
       <c r="C29" s="6">
         <v>24</v>
@@ -2926,13 +2939,13 @@
       <c r="K29" s="2">
         <v>1</v>
       </c>
-      <c r="L29" s="25" t="s">
+      <c r="L29" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="10"/>
     </row>
-    <row r="30" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B30" s="2"/>
       <c r="C30" s="6">
         <v>25</v>
@@ -2959,13 +2972,13 @@
       <c r="K30" s="2">
         <v>1</v>
       </c>
-      <c r="L30" s="25" t="s">
+      <c r="L30" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="10"/>
     </row>
-    <row r="31" spans="1:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B31" s="2"/>
       <c r="C31" s="6">
         <v>26</v>
@@ -2992,13 +3005,13 @@
       <c r="K31" s="2">
         <v>1</v>
       </c>
-      <c r="L31" s="25" t="s">
+      <c r="L31" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="10"/>
     </row>
-    <row r="32" spans="1:14" ht="253.75" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:14" ht="252" x14ac:dyDescent="0.45">
       <c r="B32" s="2"/>
       <c r="C32" s="6">
         <v>27</v>
@@ -3025,13 +3038,13 @@
       <c r="K32" s="2">
         <v>1</v>
       </c>
-      <c r="L32" s="25" t="s">
+      <c r="L32" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="10"/>
     </row>
-    <row r="33" spans="2:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B33" s="2"/>
       <c r="C33" s="6">
         <v>28</v>
@@ -3058,13 +3071,13 @@
       <c r="K33" s="2">
         <v>1</v>
       </c>
-      <c r="L33" s="25" t="s">
+      <c r="L33" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="10"/>
     </row>
-    <row r="34" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B34" s="2"/>
       <c r="C34" s="6">
         <v>29</v>
@@ -3093,13 +3106,13 @@
       <c r="K34" s="2">
         <v>1</v>
       </c>
-      <c r="L34" s="25" t="s">
+      <c r="L34" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="10"/>
     </row>
-    <row r="35" spans="2:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B35" s="2"/>
       <c r="C35" s="6">
         <v>30</v>
@@ -3126,13 +3139,13 @@
       <c r="K35" s="2">
         <v>1</v>
       </c>
-      <c r="L35" s="25" t="s">
+      <c r="L35" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="10"/>
     </row>
-    <row r="36" spans="2:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B36" s="2"/>
       <c r="C36" s="6">
         <v>31</v>
@@ -3159,13 +3172,13 @@
       <c r="K36" s="2">
         <v>1</v>
       </c>
-      <c r="L36" s="25" t="s">
+      <c r="L36" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="10"/>
     </row>
-    <row r="37" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B37" s="2"/>
       <c r="C37" s="6">
         <v>32</v>
@@ -3192,13 +3205,13 @@
       <c r="K37" s="2">
         <v>1</v>
       </c>
-      <c r="L37" s="25" t="s">
+      <c r="L37" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="10"/>
     </row>
-    <row r="38" spans="2:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B38" s="2"/>
       <c r="C38" s="6">
         <v>33</v>
@@ -3225,13 +3238,13 @@
       <c r="K38" s="2">
         <v>1</v>
       </c>
-      <c r="L38" s="25" t="s">
+      <c r="L38" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="10"/>
     </row>
-    <row r="39" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B39" s="2"/>
       <c r="C39" s="6">
         <v>34</v>
@@ -3260,13 +3273,13 @@
       <c r="K39" s="2">
         <v>1</v>
       </c>
-      <c r="L39" s="25" t="s">
+      <c r="L39" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="10"/>
     </row>
-    <row r="40" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B40" s="2"/>
       <c r="C40" s="6">
         <v>35</v>
@@ -3293,13 +3306,13 @@
       <c r="K40" s="2">
         <v>1</v>
       </c>
-      <c r="L40" s="25" t="s">
+      <c r="L40" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="10"/>
     </row>
-    <row r="41" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B41" s="2"/>
       <c r="C41" s="6">
         <v>36</v>
@@ -3328,13 +3341,13 @@
       <c r="K41" s="2">
         <v>1</v>
       </c>
-      <c r="L41" s="25" t="s">
+      <c r="L41" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="10"/>
     </row>
-    <row r="42" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B42" s="2"/>
       <c r="C42" s="6">
         <v>37</v>
@@ -3361,13 +3374,13 @@
       <c r="K42" s="2">
         <v>1</v>
       </c>
-      <c r="L42" s="25" t="s">
+      <c r="L42" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="10"/>
     </row>
-    <row r="43" spans="2:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B43" s="2"/>
       <c r="C43" s="6">
         <v>38</v>
@@ -3396,13 +3409,13 @@
       <c r="K43" s="2">
         <v>1</v>
       </c>
-      <c r="L43" s="25" t="s">
+      <c r="L43" s="23" t="s">
         <v>111</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="10"/>
     </row>
-    <row r="44" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:14" ht="20.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="1"/>
@@ -3414,22 +3427,22 @@
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" spans="2:14" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:14" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B45" s="16"/>
-      <c r="C45" s="22" t="s">
+      <c r="C45" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D45" s="22"/>
+      <c r="D45" s="25"/>
       <c r="E45" s="17" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B46" s="18"/>
-      <c r="C46" s="21" t="s">
+      <c r="C46" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D46" s="21"/>
+      <c r="D46" s="24"/>
       <c r="E46" s="17" t="s">
         <v>3</v>
       </c>
@@ -3441,12 +3454,12 @@
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
     </row>
-    <row r="47" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="19"/>
-      <c r="C47" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="21"/>
+      <c r="C47" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="24"/>
       <c r="E47" s="17" t="s">
         <v>112</v>
       </c>
@@ -3458,7 +3471,7 @@
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
     </row>
-    <row r="48" spans="2:14" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:14" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -3470,7 +3483,7 @@
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
     </row>
-    <row r="49" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="10"/>
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
@@ -3478,7 +3491,7 @@
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
     </row>
-    <row r="50" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
@@ -3491,7 +3504,7 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -3504,7 +3517,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
@@ -3517,7 +3530,7 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
@@ -3530,7 +3543,7 @@
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
@@ -3543,7 +3556,7 @@
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
@@ -3556,7 +3569,7 @@
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
@@ -3569,7 +3582,7 @@
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
@@ -3582,7 +3595,7 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
@@ -3595,7 +3608,7 @@
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
@@ -3608,7 +3621,7 @@
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
     </row>
-    <row r="60" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
@@ -3621,7 +3634,7 @@
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
     </row>
-    <row r="61" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
@@ -3634,7 +3647,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
@@ -3647,7 +3660,7 @@
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
     </row>
-    <row r="63" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
@@ -3660,7 +3673,7 @@
       <c r="K63" s="6"/>
       <c r="L63" s="6"/>
     </row>
-    <row r="64" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
@@ -3673,7 +3686,7 @@
       <c r="K64" s="6"/>
       <c r="L64" s="6"/>
     </row>
-    <row r="65" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
@@ -3686,7 +3699,7 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
@@ -3699,7 +3712,7 @@
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
     </row>
-    <row r="67" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
@@ -3712,7 +3725,7 @@
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
     </row>
-    <row r="68" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
@@ -3725,7 +3738,7 @@
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
     </row>
-    <row r="69" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
@@ -3738,7 +3751,7 @@
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
     </row>
-    <row r="70" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
@@ -3770,15 +3783,6 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="I43:J43">
     <cfRule type="iconSet" priority="3">
-      <iconSet iconSet="3Symbols2" showValue="0">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7:L7">
-    <cfRule type="iconSet" priority="16">
       <iconSet iconSet="3Symbols2" showValue="0">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="0"/>
@@ -3903,6 +3907,15 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I7:L7">
+    <cfRule type="iconSet" priority="16">
+      <iconSet iconSet="3Symbols2" showValue="0">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K42">
     <cfRule type="iconSet" priority="2">
       <iconSet iconSet="3Symbols2" showValue="0">

--- a/_Learn/Packaging.tutorial/OS.11/24H2/Expand/Install/Report.Overview.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/24H2/Expand/Install/Report.Overview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YiSolutions\_Learn\Packaging.tutorial\OS.11\25H2\Expand\Install\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YiSolutions\_Learn\Packaging.tutorial\OS.11\24H2\Expand\Install\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA814A47-424E-4384-A420-0491A8DA9EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF6A072-3197-4697-AA38-2E91BD510A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="32220" windowHeight="19500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report.Overview" sheetId="5" r:id="rId1"/>
@@ -31,9 +31,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -581,9 +578,18 @@
   </si>
   <si>
     <t xml:space="preserve">
-en-us_windows_11_consumer_editions_version_25h2_x64_dvd_9934ee4c.iso
-en-us_windows_11_business_editions_version_25h2_x64_dvd_41c521e7.iso
-en-us_windows_11_iot_enterprise_version_25h2_x64_dvd_67098cd6.iso
+en-US
+ar-EG
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.6584
+Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.6584
+Microsoft-Windows-LanguageFeatures-TextToSpeech-ar-eg-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+Microsoft-Windows-LanguageFeatures-TextToSpeech-ar-eg-Package~31bf3856ad364e35~amd64~~10.0.26100.6584
 </t>
   </si>
   <si>
@@ -603,22 +609,19 @@
 13. Windows 11 Enterprise N
 14. Windows 11 IoT Enterprise
 15. Windows 11 IoT Enterprise Subscription
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-en-US
-ar-EG
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
-Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.6584
-Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
-Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.6584
-Microsoft-Windows-LanguageFeatures-TextToSpeech-ar-eg-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
-Microsoft-Windows-LanguageFeatures-TextToSpeech-ar-eg-Package~31bf3856ad364e35~amd64~~10.0.26100.6584
+16. Windows 11 Enterprise LTSC
+17. Windows 11 Enterprise N LTSC
+18. Windows 11 IoT Enterprise LTSC
+19. Windows 11 IoT Enterprise Subscription LTSC
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+en-us_windows_11_consumer_editions_version_25h2_x64_dvd_9934ee4c.iso
+en-us_windows_11_business_editions_version_25h2_x64_dvd_41c521e7.iso
+en-us_windows_11_iot_enterprise_version_25h2_x64_dvd_67098cd6.iso
+en-us_windows_11_enterprise_ltsc_2024_x64_dvd_965cfb00.iso
+en-us_windows_11_iot_enterprise_ltsc_2024_x64_dvd_f6b14814.iso
 </t>
   </si>
 </sst>
@@ -2023,24 +2026,24 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N70"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="84.6640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="50.3984375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="20.53125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="120.6640625" style="6" customWidth="1"/>
-    <col min="9" max="11" width="16.6640625" style="6" customWidth="1"/>
-    <col min="12" max="12" width="25.6640625" style="6" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" style="10" customWidth="1"/>
-    <col min="14" max="14" width="2.6640625" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="9.1328125" style="4" hidden="1"/>
+    <col min="1" max="1" width="2.6328125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="0.81640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="84.6328125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="50.36328125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="20.54296875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="16.6328125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="120.6328125" style="6" customWidth="1"/>
+    <col min="9" max="11" width="16.6328125" style="6" customWidth="1"/>
+    <col min="12" max="12" width="25.6328125" style="6" customWidth="1"/>
+    <col min="13" max="13" width="16.6328125" style="10" customWidth="1"/>
+    <col min="14" max="14" width="2.6328125" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="9.08984375" style="4" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2055,7 +2058,7 @@
       <c r="L1" s="5"/>
       <c r="M1" s="4"/>
     </row>
-    <row r="2" spans="1:14" ht="80.2" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:14" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4"/>
       <c r="C2" s="20" t="s">
         <v>70</v>
@@ -2074,7 +2077,7 @@
       </c>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -2088,7 +2091,7 @@
       <c r="L3" s="5"/>
       <c r="M3" s="4"/>
     </row>
-    <row r="4" spans="1:14" ht="5.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -2101,7 +2104,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="21"/>
     </row>
-    <row r="5" spans="1:14" ht="62.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" ht="62.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="14"/>
       <c r="C5" s="14" t="s">
         <v>7</v>
@@ -2138,16 +2141,16 @@
       </c>
       <c r="N5" s="10"/>
     </row>
-    <row r="6" spans="1:14" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" ht="400" x14ac:dyDescent="0.35">
       <c r="B6" s="2"/>
       <c r="C6" s="6">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>14</v>
@@ -2171,7 +2174,7 @@
       <c r="M6" s="3"/>
       <c r="N6" s="10"/>
     </row>
-    <row r="7" spans="1:14" ht="157.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" ht="160" x14ac:dyDescent="0.35">
       <c r="B7" s="2"/>
       <c r="C7" s="6">
         <v>2</v>
@@ -2186,10 +2189,10 @@
         <v>6</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -2206,7 +2209,7 @@
       <c r="M7" s="3"/>
       <c r="N7" s="10"/>
     </row>
-    <row r="8" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B8" s="2"/>
       <c r="C8" s="6">
         <v>3</v>
@@ -2241,7 +2244,7 @@
       <c r="M8" s="3"/>
       <c r="N8" s="10"/>
     </row>
-    <row r="9" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B9" s="2"/>
       <c r="C9" s="6">
         <v>4</v>
@@ -2274,7 +2277,7 @@
       <c r="M9" s="3"/>
       <c r="N9" s="10"/>
     </row>
-    <row r="10" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B10" s="2"/>
       <c r="C10" s="6">
         <v>5</v>
@@ -2309,7 +2312,7 @@
       <c r="M10" s="3"/>
       <c r="N10" s="10"/>
     </row>
-    <row r="11" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B11" s="2"/>
       <c r="C11" s="6">
         <v>6</v>
@@ -2342,7 +2345,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B12" s="2"/>
       <c r="C12" s="6">
         <v>7</v>
@@ -2377,7 +2380,7 @@
       <c r="M12" s="2"/>
       <c r="N12" s="10"/>
     </row>
-    <row r="13" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B13" s="2"/>
       <c r="C13" s="6">
         <v>8</v>
@@ -2410,7 +2413,7 @@
       <c r="M13" s="2"/>
       <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="1:14" ht="252" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:14" ht="256" x14ac:dyDescent="0.35">
       <c r="B14" s="2"/>
       <c r="C14" s="6">
         <v>9</v>
@@ -2443,7 +2446,7 @@
       <c r="M14" s="2"/>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="1:14" ht="157.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:14" ht="160" x14ac:dyDescent="0.35">
       <c r="B15" s="2"/>
       <c r="C15" s="6">
         <v>10</v>
@@ -2476,7 +2479,7 @@
       <c r="M15" s="2"/>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B16" s="2"/>
       <c r="C16" s="6">
         <v>11</v>
@@ -2509,7 +2512,7 @@
       <c r="M16" s="2"/>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B17" s="2"/>
       <c r="C17" s="6">
         <v>12</v>
@@ -2542,7 +2545,7 @@
       <c r="M17" s="2"/>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:14" ht="144" x14ac:dyDescent="0.35">
       <c r="B18" s="2"/>
       <c r="C18" s="6">
         <v>13</v>
@@ -2577,7 +2580,7 @@
       <c r="M18" s="2"/>
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="1:14" ht="252" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:14" ht="256" x14ac:dyDescent="0.35">
       <c r="B19" s="2"/>
       <c r="C19" s="6">
         <v>14</v>
@@ -2610,7 +2613,7 @@
       <c r="M19" s="2"/>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:14" ht="144" x14ac:dyDescent="0.35">
       <c r="B20" s="2"/>
       <c r="C20" s="6">
         <v>15</v>
@@ -2645,7 +2648,7 @@
       <c r="M20" s="2"/>
       <c r="N20" s="10"/>
     </row>
-    <row r="21" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B21" s="2"/>
       <c r="C21" s="6">
         <v>16</v>
@@ -2678,7 +2681,7 @@
       <c r="M21" s="2"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B22" s="2"/>
       <c r="C22" s="6">
         <v>17</v>
@@ -2711,7 +2714,7 @@
       <c r="M22" s="2"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B23" s="2"/>
       <c r="C23" s="6">
         <v>18</v>
@@ -2744,7 +2747,7 @@
       <c r="M23" s="2"/>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:14" ht="144" x14ac:dyDescent="0.35">
       <c r="B24" s="2"/>
       <c r="C24" s="6">
         <v>19</v>
@@ -2777,7 +2780,7 @@
       <c r="M24" s="2"/>
       <c r="N24" s="10"/>
     </row>
-    <row r="25" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:14" ht="144" x14ac:dyDescent="0.35">
       <c r="B25" s="2"/>
       <c r="C25" s="6">
         <v>20</v>
@@ -2810,7 +2813,7 @@
       <c r="M25" s="2"/>
       <c r="N25" s="10"/>
     </row>
-    <row r="26" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B26" s="2"/>
       <c r="C26" s="6">
         <v>21</v>
@@ -2843,7 +2846,7 @@
       <c r="M26" s="2"/>
       <c r="N26" s="10"/>
     </row>
-    <row r="27" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B27" s="2"/>
       <c r="C27" s="6">
         <v>22</v>
@@ -2876,7 +2879,7 @@
       <c r="M27" s="2"/>
       <c r="N27" s="10"/>
     </row>
-    <row r="28" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="A28" s="10" t="s">
         <v>61</v>
       </c>
@@ -2912,7 +2915,7 @@
       <c r="M28" s="2"/>
       <c r="N28" s="10"/>
     </row>
-    <row r="29" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B29" s="2"/>
       <c r="C29" s="6">
         <v>24</v>
@@ -2945,7 +2948,7 @@
       <c r="M29" s="2"/>
       <c r="N29" s="10"/>
     </row>
-    <row r="30" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B30" s="2"/>
       <c r="C30" s="6">
         <v>25</v>
@@ -2978,7 +2981,7 @@
       <c r="M30" s="2"/>
       <c r="N30" s="10"/>
     </row>
-    <row r="31" spans="1:14" ht="157.5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:14" ht="160" x14ac:dyDescent="0.35">
       <c r="B31" s="2"/>
       <c r="C31" s="6">
         <v>26</v>
@@ -3011,7 +3014,7 @@
       <c r="M31" s="2"/>
       <c r="N31" s="10"/>
     </row>
-    <row r="32" spans="1:14" ht="252" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:14" ht="256" x14ac:dyDescent="0.35">
       <c r="B32" s="2"/>
       <c r="C32" s="6">
         <v>27</v>
@@ -3044,7 +3047,7 @@
       <c r="M32" s="2"/>
       <c r="N32" s="10"/>
     </row>
-    <row r="33" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B33" s="2"/>
       <c r="C33" s="6">
         <v>28</v>
@@ -3077,7 +3080,7 @@
       <c r="M33" s="2"/>
       <c r="N33" s="10"/>
     </row>
-    <row r="34" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:14" ht="160" x14ac:dyDescent="0.35">
       <c r="B34" s="2"/>
       <c r="C34" s="6">
         <v>29</v>
@@ -3112,7 +3115,7 @@
       <c r="M34" s="2"/>
       <c r="N34" s="10"/>
     </row>
-    <row r="35" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B35" s="2"/>
       <c r="C35" s="6">
         <v>30</v>
@@ -3145,7 +3148,7 @@
       <c r="M35" s="2"/>
       <c r="N35" s="10"/>
     </row>
-    <row r="36" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B36" s="2"/>
       <c r="C36" s="6">
         <v>31</v>
@@ -3178,7 +3181,7 @@
       <c r="M36" s="2"/>
       <c r="N36" s="10"/>
     </row>
-    <row r="37" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:14" ht="160" x14ac:dyDescent="0.35">
       <c r="B37" s="2"/>
       <c r="C37" s="6">
         <v>32</v>
@@ -3211,7 +3214,7 @@
       <c r="M37" s="2"/>
       <c r="N37" s="10"/>
     </row>
-    <row r="38" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:14" ht="240" x14ac:dyDescent="0.35">
       <c r="B38" s="2"/>
       <c r="C38" s="6">
         <v>33</v>
@@ -3244,7 +3247,7 @@
       <c r="M38" s="2"/>
       <c r="N38" s="10"/>
     </row>
-    <row r="39" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:14" ht="160" x14ac:dyDescent="0.35">
       <c r="B39" s="2"/>
       <c r="C39" s="6">
         <v>34</v>
@@ -3279,7 +3282,7 @@
       <c r="M39" s="2"/>
       <c r="N39" s="10"/>
     </row>
-    <row r="40" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:14" ht="160" x14ac:dyDescent="0.35">
       <c r="B40" s="2"/>
       <c r="C40" s="6">
         <v>35</v>
@@ -3312,7 +3315,7 @@
       <c r="M40" s="2"/>
       <c r="N40" s="10"/>
     </row>
-    <row r="41" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:14" ht="160" x14ac:dyDescent="0.35">
       <c r="B41" s="2"/>
       <c r="C41" s="6">
         <v>36</v>
@@ -3347,7 +3350,7 @@
       <c r="M41" s="2"/>
       <c r="N41" s="10"/>
     </row>
-    <row r="42" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:14" ht="160" x14ac:dyDescent="0.35">
       <c r="B42" s="2"/>
       <c r="C42" s="6">
         <v>37</v>
@@ -3380,7 +3383,7 @@
       <c r="M42" s="2"/>
       <c r="N42" s="10"/>
     </row>
-    <row r="43" spans="2:14" ht="141.75" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:14" ht="144" x14ac:dyDescent="0.35">
       <c r="B43" s="2"/>
       <c r="C43" s="6">
         <v>38</v>
@@ -3415,7 +3418,7 @@
       <c r="M43" s="2"/>
       <c r="N43" s="10"/>
     </row>
-    <row r="44" spans="2:14" ht="20.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="1"/>
@@ -3427,7 +3430,7 @@
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" spans="2:14" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="2:14" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B45" s="16"/>
       <c r="C45" s="25" t="s">
         <v>2</v>
@@ -3437,7 +3440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="46" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B46" s="18"/>
       <c r="C46" s="24" t="s">
         <v>0</v>
@@ -3454,7 +3457,7 @@
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
     </row>
-    <row r="47" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="47" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="19"/>
       <c r="C47" s="24" t="s">
         <v>1</v>
@@ -3471,7 +3474,7 @@
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
     </row>
-    <row r="48" spans="2:14" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:14" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -3483,7 +3486,7 @@
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
     </row>
-    <row r="49" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C49" s="10"/>
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
@@ -3491,7 +3494,7 @@
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
     </row>
-    <row r="50" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
@@ -3504,7 +3507,7 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -3517,7 +3520,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
@@ -3530,7 +3533,7 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
@@ -3543,7 +3546,7 @@
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
@@ -3556,7 +3559,7 @@
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
@@ -3569,7 +3572,7 @@
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
@@ -3582,7 +3585,7 @@
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
@@ -3595,7 +3598,7 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
@@ -3608,7 +3611,7 @@
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
@@ -3621,7 +3624,7 @@
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
     </row>
-    <row r="60" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
@@ -3634,7 +3637,7 @@
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
     </row>
-    <row r="61" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
@@ -3647,7 +3650,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
@@ -3660,7 +3663,7 @@
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
     </row>
-    <row r="63" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
@@ -3673,7 +3676,7 @@
       <c r="K63" s="6"/>
       <c r="L63" s="6"/>
     </row>
-    <row r="64" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
@@ -3686,7 +3689,7 @@
       <c r="K64" s="6"/>
       <c r="L64" s="6"/>
     </row>
-    <row r="65" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
@@ -3699,7 +3702,7 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
@@ -3712,7 +3715,7 @@
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
     </row>
-    <row r="67" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
@@ -3725,7 +3728,7 @@
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
     </row>
-    <row r="68" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
@@ -3738,7 +3741,7 @@
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
     </row>
-    <row r="69" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
@@ -3751,7 +3754,7 @@
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
     </row>
-    <row r="70" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
